--- a/results/Int All Data -0.1/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_1_permute.xlsx
@@ -440,137 +440,137 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9341618334365673</v>
+        <v>0.9130705557745369</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9282358240891943</v>
+        <v>0.9113688833830733</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9241409989301199</v>
+        <v>0.9144400022523791</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9133813840869418</v>
+        <v>0.9111177431161666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9123779492088518</v>
+        <v>0.9036533588602962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9076119150853088</v>
+        <v>0.9142294048088293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9082493383636465</v>
+        <v>0.9210293372374571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9098901965200743</v>
+        <v>0.9234022185933892</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9075240723013682</v>
+        <v>0.9210225801002309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8960121628470071</v>
+        <v>0.9240936989695365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8970155977250971</v>
+        <v>0.9214021059744355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8970155977250971</v>
+        <v>0.9214021059744355</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8912461287234642</v>
+        <v>0.9214021059744355</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8926155752013063</v>
+        <v>0.9214426487977927</v>
       </c>
     </row>
     <row r="16">
@@ -580,137 +580,137 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9137203671377893</v>
+        <v>0.9146551044540796</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9191170674024438</v>
+        <v>0.9197803930401487</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9191170674024438</v>
+        <v>0.9197533644912439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9180933611126753</v>
+        <v>0.9231094093135874</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9208795540289431</v>
+        <v>0.9231094093135874</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9195641646489103</v>
+        <v>0.9197601216284701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9164998029168309</v>
+        <v>0.9190956698012276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9114218142913453</v>
+        <v>0.9190956698012276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9141336786981249</v>
+        <v>0.9210822681457289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9144659046117461</v>
+        <v>0.9332586294273326</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.930194267695253</v>
+        <v>0.9328655892786756</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9235092065994707</v>
+        <v>0.928865364040768</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.917888394616814</v>
+        <v>0.9241196013289037</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9192240554085253</v>
+        <v>0.9254485049833887</v>
       </c>
     </row>
     <row r="30">
@@ -720,1073 +720,1073 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9246545413593108</v>
+        <v>0.9341336786981249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9225936145053213</v>
+        <v>0.933096458133904</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8956765583647728</v>
+        <v>0.930764119601329</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8956765583647728</v>
+        <v>0.9383512585168083</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9005788614223773</v>
+        <v>0.9316594402837998</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8979413255250859</v>
+        <v>0.9330153724871897</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8932969198716144</v>
+        <v>0.9222895433301425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8989380032659497</v>
+        <v>0.9199639619347937</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9171496142800833</v>
+        <v>0.9222692719184639</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9100715130356438</v>
+        <v>0.920194830790022</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9174480545075736</v>
+        <v>0.921475308294386</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9227636691255139</v>
+        <v>0.9137259980854777</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.907663719804043</v>
+        <v>0.9113801452784503</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9086063404470972</v>
+        <v>0.9097460442592489</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8935750886874261</v>
+        <v>0.9097460442592489</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8945650092910638</v>
+        <v>0.9026476716031309</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8970133453460217</v>
+        <v>0.8980100230868855</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8977521256827524</v>
+        <v>0.8963624077932316</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8857176642828988</v>
+        <v>0.8963624077932316</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8840768061264711</v>
+        <v>0.8882943859451546</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8835891660566473</v>
+        <v>0.8732980460611521</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8833718114758714</v>
+        <v>0.8732980460611521</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8817377104566699</v>
+        <v>0.8729455487358522</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8813311560335604</v>
+        <v>0.8685387690748353</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.874436623683766</v>
+        <v>0.8641928036488541</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8682189312461288</v>
+        <v>0.8633729376654091</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8651005124162396</v>
+        <v>0.8553454586406892</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8631814854440003</v>
+        <v>0.8575967115265499</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8668629990427389</v>
+        <v>0.8485117405259306</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.856169829382285</v>
+        <v>0.8410541134072864</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8390506222197196</v>
+        <v>0.8549253899431275</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8367250408243707</v>
+        <v>0.84956923250183</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8370369953263135</v>
+        <v>0.8330266343825665</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.836020046173771</v>
+        <v>0.845121910017456</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8596351145897854</v>
+        <v>0.8689937496480657</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8606182780561968</v>
+        <v>0.8689937496480657</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8466445182724253</v>
+        <v>0.8919635114589786</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8588828199786024</v>
+        <v>0.8905873078439102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8850746100568725</v>
+        <v>0.888899149726899</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8850746100568725</v>
+        <v>0.8985055464834731</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8836713778928993</v>
+        <v>0.8922608254969311</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8803761473055915</v>
+        <v>0.8922608254969311</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8823627456500929</v>
+        <v>0.8956506560054056</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8755076299341179</v>
+        <v>0.8961529365392196</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8568635621375078</v>
+        <v>0.8925457514499691</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8595146123092516</v>
+        <v>0.8874812770989358</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8403479925671491</v>
+        <v>0.8881524860634045</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8446061152091897</v>
+        <v>0.8891694352159468</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8353037896277944</v>
+        <v>0.8895084182667943</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8356360155414156</v>
+        <v>0.8898338870431894</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8379548397995382</v>
+        <v>0.8843628582690467</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8383073371248382</v>
+        <v>0.8860307449743792</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8376969423954052</v>
+        <v>0.8880781575539163</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8420834506447435</v>
+        <v>0.8815496368038741</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8375268877752126</v>
+        <v>0.8798412072751844</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8314251928599583</v>
+        <v>0.8801734331888057</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8183602680331099</v>
+        <v>0.8842412297989752</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8045768342812096</v>
+        <v>0.8795360099104679</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8073956866940706</v>
+        <v>0.8767700884058787</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8004313305929387</v>
+        <v>0.8716718283687144</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8061197139478574</v>
+        <v>0.869970155977251</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8061197139478574</v>
+        <v>0.8658685736809505</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8309409313587477</v>
+        <v>0.8679362576721663</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8309409313587477</v>
+        <v>0.8689532068247086</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8683799763500197</v>
+        <v>0.851550199898643</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8616600033785686</v>
+        <v>0.8423638718396307</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8698305084745763</v>
+        <v>0.8539028098428966</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.865192859958331</v>
+        <v>0.8311166169266289</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8737226195168647</v>
+        <v>0.8311166169266289</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8737226195168647</v>
+        <v>0.8206081423503576</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8737226195168647</v>
+        <v>0.8148386733487246</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8685365166957599</v>
+        <v>0.8219708316909735</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8623672504082438</v>
+        <v>0.7516999831071569</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8627884452953432</v>
+        <v>0.7472864463089137</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8614325130919533</v>
+        <v>0.7459440283799763</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8445453009741539</v>
+        <v>0.7408390112055858</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8177994256433359</v>
+        <v>0.7513272143701786</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7223571147024044</v>
+        <v>0.7557745368545526</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7131775437806183</v>
+        <v>0.6966833718114759</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7111301312010812</v>
+        <v>0.6790765245790866</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6790967959907652</v>
+        <v>0.6732327270679656</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7494340897573062</v>
+        <v>0.6920457232952306</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7487426093811589</v>
+        <v>0.6393276648459936</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7464237851230362</v>
+        <v>0.6406768399121572</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6867424967622051</v>
+        <v>0.6549479137338814</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6710749479137339</v>
+        <v>0.6249619911031027</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6714679880623908</v>
+        <v>0.6252807027422715</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6317393997409764</v>
+        <v>0.625619685793119</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5097212680894194</v>
+        <v>0.6079317529140155</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5164671434202376</v>
+        <v>0.5241421251196576</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5070026465454136</v>
+        <v>0.5254913001858212</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5022298552846444</v>
+        <v>0.5292268708823695</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5029145785235655</v>
+        <v>0.5292268708823695</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5029145785235655</v>
+        <v>0.5288878878315221</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4954772228166001</v>
+        <v>0.5237828706571316</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5013559322033898</v>
+        <v>0.5217624866264993</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5010169491525424</v>
+        <v>0.5244743510332789</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.5153150515231714</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.5057897404133116</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.506806689565854</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.506806689565854</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.506806689565854</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.506806689565854</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.5047795483979953</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5003457401880737</v>
+        <v>0.5047795483979953</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.5040948251590742</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5003389830508475</v>
+        <v>0.503762599245453</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1796,57 +1796,57 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5010169491525424</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5010169491525424</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1856,7 +1856,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1866,7 +1866,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B156" t="n">
